--- a/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 15,53</t>
+          <t>3,79; 15,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 13,37</t>
+          <t>2,3; 13,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 12,77</t>
+          <t>-4,59; 12,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 11,07</t>
+          <t>-2,34; 10,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 3,89</t>
+          <t>-8,73; 4,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,99; -4,34</t>
+          <t>-19,89; -4,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,33</t>
+          <t>2,85; 11,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,49</t>
+          <t>-1,02; 7,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 1,92</t>
+          <t>-10,07; 2,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 81,9</t>
+          <t>15,27; 79,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 66,63</t>
+          <t>9,12; 69,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 62,01</t>
+          <t>-18,98; 63,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 32,36</t>
+          <t>-5,94; 32,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 11,08</t>
+          <t>-22,41; 11,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,5; -11,83</t>
+          <t>-51,56; -12,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 41,23</t>
+          <t>9,26; 41,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 28,47</t>
+          <t>-3,38; 26,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,99; 6,47</t>
+          <t>-33,36; 9,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 15,83</t>
+          <t>5,72; 16,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 6,07</t>
+          <t>-3,91; 6,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 1,7</t>
+          <t>-11,43; 1,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 9,77</t>
+          <t>-2,12; 9,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 1,59</t>
+          <t>-9,49; 2,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,61; -17,39</t>
+          <t>-32,45; -17,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,55</t>
+          <t>4,32; 11,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,31</t>
+          <t>-4,93; 2,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -9,35</t>
+          <t>-19,14; -8,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 63,58</t>
+          <t>19,34; 64,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 24,26</t>
+          <t>-13,54; 24,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 7,29</t>
+          <t>-38,64; 5,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 23,78</t>
+          <t>-4,63; 23,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 3,74</t>
+          <t>-20,06; 4,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,13; -42,66</t>
+          <t>-72,21; -41,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 34,88</t>
+          <t>11,87; 36,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 10,16</t>
+          <t>-13,47; 8,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,7; -28,28</t>
+          <t>-54,12; -26,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 13,16</t>
+          <t>1,75; 12,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,92</t>
+          <t>-5,5; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,24; -7,78</t>
+          <t>-18,46; -7,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 11,37</t>
+          <t>0,01; 11,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 1,61</t>
+          <t>-8,99; 1,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,65; -22,41</t>
+          <t>-34,63; -22,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,04</t>
+          <t>2,37; 10,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,16</t>
+          <t>-6,19; 1,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,95; -16,86</t>
+          <t>-24,98; -16,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 43,82</t>
+          <t>4,92; 41,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 15,73</t>
+          <t>-15,17; 16,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,26; -25,79</t>
+          <t>-50,33; -24,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 23,73</t>
+          <t>0,07; 22,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 3,4</t>
+          <t>-16,13; 2,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -45,63</t>
+          <t>-64,86; -44,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,61; 24,11</t>
+          <t>5,36; 25,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,76</t>
+          <t>-14,03; 3,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,47; -40,97</t>
+          <t>-55,97; -40,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 8,9</t>
+          <t>-3,8; 8,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 10,34</t>
+          <t>-1,92; 10,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-38,42; -14,36</t>
+          <t>-39,49; -14,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,52</t>
+          <t>1,74; 13,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 1,58</t>
+          <t>-9,8; 2,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,02; -23,18</t>
+          <t>-35,27; -23,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,88</t>
+          <t>0,73; 9,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,19</t>
+          <t>-4,42; 4,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-39,56; -21,34</t>
+          <t>-41,03; -21,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 19,74</t>
+          <t>-7,38; 18,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 23,12</t>
+          <t>-3,87; 23,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,97; -31,82</t>
+          <t>-79,21; -32,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 22,58</t>
+          <t>2,61; 22,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 2,51</t>
+          <t>-14,87; 3,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,82; -38,45</t>
+          <t>-54,56; -39,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 18,82</t>
+          <t>1,28; 17,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 7,78</t>
+          <t>-7,58; 7,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,93; -39,2</t>
+          <t>-69,04; -38,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 11,45</t>
+          <t>-1,4; 10,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -0,47</t>
+          <t>-13,67; -0,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -20,3</t>
+          <t>-33,47; -21,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,12</t>
+          <t>3,56; 14,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,6</t>
+          <t>-4,17; 7,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,26; -22,51</t>
+          <t>-32,96; -22,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,04</t>
+          <t>2,75; 11,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 1,27</t>
+          <t>-6,75; 1,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,43; -23,46</t>
+          <t>-31,0; -23,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 16,63</t>
+          <t>-1,86; 16,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -0,59</t>
+          <t>-18,43; -0,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,91; -30,02</t>
+          <t>-44,87; -30,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,78; 19,2</t>
+          <t>4,41; 19,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 10,07</t>
+          <t>-5,25; 9,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,2; -30,22</t>
+          <t>-41,14; -30,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,46; 15,3</t>
+          <t>3,61; 15,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 1,76</t>
+          <t>-8,81; 2,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,35; -32,81</t>
+          <t>-40,9; -32,23</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10,51; 21,85</t>
+          <t>10,49; 21,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,62; 16,81</t>
+          <t>5,17; 16,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-36,04; -23,35</t>
+          <t>-36,08; -23,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,66</t>
+          <t>1,59; 10,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,0</t>
+          <t>-4,57; 5,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 1,22</t>
+          <t>-31,37; -0,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,07; 13,81</t>
+          <t>7,17; 13,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,61</t>
+          <t>0,9; 8,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-31,3; -1,74</t>
+          <t>-30,96; -2,94</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,93; 29,9</t>
+          <t>13,03; 30,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5,67; 23,13</t>
+          <t>6,22; 23,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -32,01</t>
+          <t>-45,3; -32,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,73; 11,28</t>
+          <t>1,76; 11,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,79</t>
+          <t>-5,03; 5,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 1,4</t>
+          <t>-34,81; 0,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,08</t>
+          <t>8,4; 17,42</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,54</t>
+          <t>1,08; 10,43</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,17; -2,04</t>
+          <t>-36,83; -3,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,97</t>
+          <t>3,3; 13,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,09</t>
+          <t>1,07; 11,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-29,95; -16,76</t>
+          <t>-29,44; -16,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,03</t>
+          <t>3,58; 11,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,55</t>
+          <t>2,14; 10,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-27,33; -17,86</t>
+          <t>-27,99; -18,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,86</t>
+          <t>4,71; 10,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,44</t>
+          <t>2,81; 9,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-26,92; -18,73</t>
+          <t>-26,89; -19,41</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,67; 17,03</t>
+          <t>3,64; 16,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,9; 14,41</t>
+          <t>1,37; 14,31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,5; -20,16</t>
+          <t>-32,9; -19,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,71</t>
+          <t>3,89; 13,46</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,48; 12,19</t>
+          <t>2,37; 12,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,99; -20,89</t>
+          <t>-30,27; -21,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,57</t>
+          <t>5,15; 12,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,41; 10,89</t>
+          <t>3,08; 11,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,67; -21,5</t>
+          <t>-29,77; -22,44</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,12</t>
+          <t>7,03; 11,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,95</t>
+          <t>2,75; 7,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -8,91</t>
+          <t>-20,14; -8,9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,46</t>
+          <t>4,95; 9,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,08</t>
+          <t>-1,39; 3,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -7,55</t>
+          <t>-22,68; -7,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,07</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,94</t>
+          <t>1,43; 4,7</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -9,31</t>
+          <t>-18,83; -9,65</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>15,39; 28,18</t>
+          <t>15,37; 27,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6,06; 18,5</t>
+          <t>5,99; 17,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-42,66; -20,33</t>
+          <t>-44,75; -20,32</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,05</t>
+          <t>8,05; 16,51</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,24</t>
+          <t>-2,23; 5,28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,11; -12,58</t>
+          <t>-37,36; -11,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,53; 19,61</t>
+          <t>12,4; 19,49</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,62</t>
+          <t>2,72; 9,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -17,9</t>
+          <t>-35,72; -18,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,69</t>
+          <t>-13,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-7,62</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 15,57</t>
+          <t>3,48; 14,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,76</t>
+          <t>1,15; 13,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 12,88</t>
+          <t>-8,6; 6,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 10,92</t>
+          <t>-1,95; 10,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 4,05</t>
+          <t>-8,26; 4,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,89; -4,43</t>
+          <t>-20,98; -6,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,42</t>
+          <t>2,91; 11,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 7,22</t>
+          <t>-1,45; 7,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 2,59</t>
+          <t>-12,67; -2,2</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>-7,86%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-34,74%</t>
+          <t>-37,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,3%</t>
+          <t>-26,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,27; 79,87</t>
+          <t>12,95; 74,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 69,74</t>
+          <t>4,37; 64,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 63,14</t>
+          <t>-35,94; 32,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 32,87</t>
+          <t>-4,66; 32,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 11,54</t>
+          <t>-20,88; 12,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,56; -12,44</t>
+          <t>-55,43; -18,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 41,67</t>
+          <t>9,17; 42,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 26,7</t>
+          <t>-4,58; 27,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 9,34</t>
+          <t>-41,17; -7,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-6,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-23,89</t>
+          <t>-21,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,83</t>
+          <t>-13,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 16,15</t>
+          <t>6,03; 16,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 6,19</t>
+          <t>-4,46; 5,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 1,41</t>
+          <t>-11,68; -0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 9,62</t>
+          <t>-1,92; 9,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 2,0</t>
+          <t>-9,31; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,45; -17,3</t>
+          <t>-27,46; -16,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,97</t>
+          <t>4,05; 11,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 2,93</t>
+          <t>-4,37; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -8,88</t>
+          <t>-17,87; -9,88</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-17,48%</t>
+          <t>-23,63%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-54,79%</t>
+          <t>-50,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-39,66%</t>
+          <t>-38,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,34; 64,46</t>
+          <t>20,13; 65,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 24,71</t>
+          <t>-14,65; 24,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 5,96</t>
+          <t>-40,64; -0,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 23,94</t>
+          <t>-4,33; 22,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 4,98</t>
+          <t>-19,82; 4,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,21; -41,51</t>
+          <t>-59,37; -39,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 36,69</t>
+          <t>11,14; 34,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 8,87</t>
+          <t>-11,94; 9,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,12; -26,75</t>
+          <t>-48,89; -29,03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-13,04</t>
+          <t>-13,78</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-27,45</t>
+          <t>-26,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-20,5</t>
+          <t>-20,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 12,88</t>
+          <t>2,04; 12,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 5,16</t>
+          <t>-5,95; 5,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; -7,87</t>
+          <t>-18,64; -8,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 11,1</t>
+          <t>-0,14; 10,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,44</t>
+          <t>-8,78; 1,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,63; -22,03</t>
+          <t>-30,77; -21,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,23</t>
+          <t>2,21; 10,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 1,41</t>
+          <t>-6,31; 1,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,98; -16,8</t>
+          <t>-23,65; -16,79</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-38,8%</t>
+          <t>-41,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-53,36%</t>
+          <t>-50,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-47,83%</t>
+          <t>-47,26%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,92; 41,54</t>
+          <t>5,93; 41,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 16,66</t>
+          <t>-16,12; 16,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,33; -24,68</t>
+          <t>-52,33; -28,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 22,83</t>
+          <t>-0,07; 21,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 2,95</t>
+          <t>-16,38; 2,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,86; -44,96</t>
+          <t>-56,75; -43,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 25,17</t>
+          <t>4,77; 25,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 3,52</t>
+          <t>-14,03; 4,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,97; -40,77</t>
+          <t>-52,86; -40,87</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-25,5</t>
+          <t>-17,44</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-28,6</t>
+          <t>-27,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-27,72</t>
+          <t>-22,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,15</t>
+          <t>-3,15; 9,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 10,3</t>
+          <t>-1,47; 9,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -14,89</t>
+          <t>-23,12; -11,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 13,48</t>
+          <t>1,94; 13,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 2,01</t>
+          <t>-10,06; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,27; -23,34</t>
+          <t>-32,15; -22,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,47</t>
+          <t>1,19; 9,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,0</t>
+          <t>-3,92; 4,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -21,19</t>
+          <t>-26,0; -18,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-53,8%</t>
+          <t>-36,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,27%</t>
+          <t>-43,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,15%</t>
+          <t>-40,44%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 18,46</t>
+          <t>-6,17; 20,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 23,43</t>
+          <t>-2,84; 22,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,21; -32,24</t>
+          <t>-45,27; -25,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 22,34</t>
+          <t>2,99; 23,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 3,27</t>
+          <t>-15,14; 3,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,56; -39,02</t>
+          <t>-48,78; -37,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 17,84</t>
+          <t>2,02; 18,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 7,69</t>
+          <t>-6,85; 8,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,04; -38,85</t>
+          <t>-45,2; -34,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-26,84</t>
+          <t>-28,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-27,7</t>
+          <t>-27,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-27,37</t>
+          <t>-28,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 10,91</t>
+          <t>-1,51; 11,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -0,47</t>
+          <t>-13,2; 0,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-33,47; -21,09</t>
+          <t>-33,75; -22,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,26</t>
+          <t>3,58; 14,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 7,03</t>
+          <t>-4,31; 6,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,96; -22,48</t>
+          <t>-32,97; -22,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,25</t>
+          <t>2,87; 10,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,98</t>
+          <t>-7,07; 1,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,0; -23,12</t>
+          <t>-31,9; -23,94</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-37,87%</t>
+          <t>-39,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-35,79%</t>
+          <t>-35,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,89%</t>
+          <t>-37,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 16,58</t>
+          <t>-2,05; 16,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -0,67</t>
+          <t>-17,82; 0,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,87; -30,92</t>
+          <t>-46,17; -32,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,41; 19,27</t>
+          <t>4,73; 19,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 9,47</t>
+          <t>-5,52; 9,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -30,18</t>
+          <t>-41,06; -30,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,61; 15,71</t>
+          <t>3,78; 15,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,79</t>
+          <t>-9,33; 2,65</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,9; -32,23</t>
+          <t>-41,87; -33,45</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-29,81</t>
+          <t>-30,46</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-15,61</t>
+          <t>-29,13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-19,99</t>
+          <t>-30,01</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10,49; 21,86</t>
+          <t>10,42; 21,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,17; 16,9</t>
+          <t>4,42; 16,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-36,08; -23,48</t>
+          <t>-36,14; -23,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,59; 10,0</t>
+          <t>1,98; 10,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,03</t>
+          <t>-4,46; 4,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-31,37; -0,06</t>
+          <t>-33,67; -24,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,96</t>
+          <t>6,78; 13,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,47</t>
+          <t>1,11; 8,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-30,96; -2,94</t>
+          <t>-33,84; -25,92</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-38,73%</t>
+          <t>-39,59%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-17,63%</t>
+          <t>-32,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-24,03%</t>
+          <t>-36,07%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13,03; 30,55</t>
+          <t>12,9; 29,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,22; 23,1</t>
+          <t>5,57; 22,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -32,07</t>
+          <t>-45,99; -32,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,81</t>
+          <t>2,17; 11,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,87</t>
+          <t>-4,91; 5,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 0,02</t>
+          <t>-37,32; -27,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,4; 17,42</t>
+          <t>7,96; 17,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,43</t>
+          <t>1,28; 10,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -3,5</t>
+          <t>-39,93; -32,02</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-23,37</t>
+          <t>-23,93</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-23,1</t>
+          <t>-23,72</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-23,25</t>
+          <t>-23,85</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,3; 13,55</t>
+          <t>3,21; 13,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,81</t>
+          <t>1,37; 12,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-29,44; -16,52</t>
+          <t>-29,74; -16,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,58; 11,71</t>
+          <t>3,52; 11,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,59</t>
+          <t>2,12; 10,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-27,99; -18,29</t>
+          <t>-28,11; -18,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,67</t>
+          <t>4,53; 10,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,58</t>
+          <t>3,16; 9,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-26,89; -19,41</t>
+          <t>-27,66; -19,93</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-26,86%</t>
+          <t>-27,49%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-25,69%</t>
+          <t>-26,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-26,18%</t>
+          <t>-26,85%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,35</t>
+          <t>3,6; 16,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,37; 14,31</t>
+          <t>1,59; 14,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -19,82</t>
+          <t>-33,4; -20,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,46</t>
+          <t>3,79; 13,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,37; 12,45</t>
+          <t>2,34; 12,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-30,27; -21,05</t>
+          <t>-30,8; -21,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,3</t>
+          <t>5,05; 12,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,1</t>
+          <t>3,52; 10,91</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,77; -22,44</t>
+          <t>-30,42; -22,9</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>-11,48</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-18,24</t>
+          <t>-20,69</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-15,28</t>
+          <t>-16,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,76</t>
+          <t>6,9; 11,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,73</t>
+          <t>2,69; 7,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -8,9</t>
+          <t>-14,1; -9,22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,7</t>
+          <t>4,84; 9,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,13</t>
+          <t>-1,51; 3,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,68; -7,17</t>
+          <t>-22,65; -18,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>6,67; 10,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,7</t>
+          <t>1,39; 4,82</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -9,65</t>
+          <t>-17,8; -14,42</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-28,04%</t>
+          <t>-25,87%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-30,2%</t>
+          <t>-34,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-29,11%</t>
+          <t>-30,69%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>15,37; 27,37</t>
+          <t>15,06; 27,68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,99</t>
+          <t>5,84; 18,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-44,75; -20,32</t>
+          <t>-30,82; -21,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,05; 16,51</t>
+          <t>7,81; 16,09</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,28</t>
+          <t>-2,47; 5,6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,36; -11,81</t>
+          <t>-36,92; -31,5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,4; 19,49</t>
+          <t>12,43; 19,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,18</t>
+          <t>2,59; 9,35</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -18,52</t>
+          <t>-33,44; -27,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
